--- a/site/leagues/betclic/2026_2027/xlsx/opponent_shooting_packs/opponent_shooting_pack_PSC.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/opponent_shooting_packs/opponent_shooting_pack_PSC.xlsx
@@ -425,7 +425,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +482,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>G. Rosado (12 L)</t>
+          <t>M. Landdeck (26 L)</t>
         </is>
       </c>
     </row>
@@ -494,7 +494,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M. Landdeck (8.0 3PA)</t>
+          <t>M. Landdeck (16.0 3PA)</t>
         </is>
       </c>
     </row>
@@ -506,7 +506,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>G. Rosado (1.333)</t>
+          <t>G. Rosado (1.455)</t>
         </is>
       </c>
     </row>
@@ -518,7 +518,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Paint Non-RA (25 L)</t>
+          <t>Above the Break 3 (38 L)</t>
         </is>
       </c>
     </row>
@@ -530,7 +530,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Restricted Area (70.0%)</t>
+          <t>Restricted Area (57.1%)</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH4"/>
+  <dimension ref="A1:BH8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -566,7 +566,7 @@
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="21" customWidth="1" min="19" max="19"/>
     <col width="18" customWidth="1" min="20" max="20"/>
     <col width="19" customWidth="1" min="21" max="21"/>
     <col width="16" customWidth="1" min="22" max="22"/>
@@ -930,134 +930,134 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PSC_G._ROSADO</t>
+          <t>PSC_M._LANDDECK</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>322806</t>
+          <t>322702</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>G. Rosado</t>
+          <t>M. Landdeck</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>26</v>
+      </c>
+      <c r="H2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I2" t="n">
         <v>12</v>
       </c>
-      <c r="H2" t="n">
-        <v>8</v>
-      </c>
-      <c r="I2" t="n">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>19.2%</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>10</v>
+      </c>
+      <c r="L2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
         <v>16</v>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>11</v>
-      </c>
-      <c r="L2" t="n">
-        <v>8</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>72.7%</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>1</v>
-      </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>61.5%</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>0.4615384615384616</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>12</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>91.7%</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>8.3%</t>
-        </is>
-      </c>
-      <c r="S2" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="V2" t="n">
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
         <v>6</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="Y2" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AB2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AE2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AH2" t="n">
-        <v>5</v>
-      </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr"/>
@@ -1065,37 +1065,37 @@
       <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="AN2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
         <v>6</v>
       </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AQ2" t="n">
-        <v>5</v>
-      </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -1107,18 +1107,18 @@
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>700.0%</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AY2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="BA2" t="n">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>800.0%</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="BD2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1142,15 +1142,15 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>700.0%</t>
         </is>
       </c>
       <c r="BG2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
     </row>
@@ -1172,217 +1172,227 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PSC_L._RAHAMA</t>
+          <t>PSC_G._ROSADO</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>296104</t>
+          <t>322806</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>L. Rahama</t>
+          <t>G. Rosado</t>
         </is>
       </c>
       <c r="G3" t="n">
+        <v>22</v>
+      </c>
+      <c r="H3" t="n">
+        <v>16</v>
+      </c>
+      <c r="I3" t="n">
+        <v>32</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>72.7%</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>20</v>
+      </c>
+      <c r="L3" t="n">
+        <v>16</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>90.9%</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>9.1%</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>1.454545454545455</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
         <v>12</v>
       </c>
-      <c r="H3" t="n">
-        <v>3</v>
-      </c>
-      <c r="I3" t="n">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>91.7%</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
         <v>7</v>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L3" t="n">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
         <v>2</v>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
-        <v>4</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1</v>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="S3" t="n">
-        <v>0.5833333333333334</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AE3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>91.7%</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
         <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="V3" t="n">
-        <v>6</v>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="Y3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AB3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AE3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
+      <c r="AH3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>91.7%</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="AN3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
+      <c r="AQ3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="AQ3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="AT3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AV3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="AV3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>300.0%</t>
-        </is>
-      </c>
       <c r="AX3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AY3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BA3" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="BA3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB3" t="inlineStr">
+      <c r="BC3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>700.0%</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="BG3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH3" t="inlineStr">
         <is>
           <t>600.0%</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>3</v>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>400.0%</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>300.0%</t>
-        </is>
-      </c>
-      <c r="BG3" t="n">
-        <v>3</v>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -1404,121 +1414,121 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PSC_M._LANDDECK</t>
+          <t>PSC_J._GREWAL</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>322702</t>
+          <t>297507</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>M. Landdeck</t>
+          <t>J. Grewal</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="K4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L4" t="n">
         <v>2</v>
       </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="N4" t="n">
         <v>8</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>52.9%</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>47.1%</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>0.7647058823529411</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>5</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>25.0%</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="S4" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="V4" t="n">
-        <v>6</v>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="Y4" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="AB4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
       <c r="AE4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr"/>
@@ -1533,37 +1543,37 @@
         </is>
       </c>
       <c r="AN4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AT4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>33.3%</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AQ4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="AT4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>0.0%</t>
         </is>
       </c>
       <c r="AV4" t="n">
@@ -1571,18 +1581,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AY4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="BA4" t="n">
@@ -1594,27 +1604,955 @@
         </is>
       </c>
       <c r="BC4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BG4" t="n">
         <v>4</v>
       </c>
-      <c r="BD4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BE4" t="inlineStr">
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Portimonense SC</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PSC_T._COLEMAN</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>322815</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>T. Coleman</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>15</v>
+      </c>
+      <c r="H5" t="n">
+        <v>9</v>
+      </c>
+      <c r="I5" t="n">
+        <v>19</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>14</v>
+      </c>
+      <c r="L5" t="n">
+        <v>8</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>93.3%</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>6.7%</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>1.266666666666667</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>9</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>55.6%</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>55.6%</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>55.6%</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AT5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AV5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="AX5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="BA5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="BC5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>9</v>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="BG5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Portimonense SC</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PSC_D._FRAGOSO</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>143839</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>D. Fragoso</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>15</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" t="n">
+        <v>8</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>26.7%</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>11</v>
+      </c>
+      <c r="L6" t="n">
+        <v>4</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>4</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>73.3%</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>26.7%</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>0.5333333333333333</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>6</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AE6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AT6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AV6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="AX6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BA6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>700.0%</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BG6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Portimonense SC</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PSC_P._BASTOS</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>155174</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>P. Bastos</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H7" t="n">
+        <v>5</v>
+      </c>
+      <c r="I7" t="n">
+        <v>15</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>10</v>
+      </c>
+      <c r="O7" t="n">
+        <v>5</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>5</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="AT7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AV7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="AX7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="BA7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB7" t="inlineStr">
         <is>
           <t>400.0%</t>
         </is>
       </c>
-      <c r="BF4" t="inlineStr">
+      <c r="BC7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE7" t="inlineStr">
         <is>
           <t>200.0%</t>
         </is>
       </c>
-      <c r="BG4" t="n">
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="BG7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Portimonense SC</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PSC_L._RAHAMA</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>296104</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>L. Rahama</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>12</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" t="n">
+        <v>7</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L8" t="n">
         <v>2</v>
       </c>
-      <c r="BH4" t="inlineStr">
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>4</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>6</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC8" t="inlineStr">
         <is>
           <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AE8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AN8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AQ8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AT8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AV8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="AX8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BA8" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>700.0%</t>
+        </is>
+      </c>
+      <c r="BC8" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BG8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>400.0%</t>
         </is>
       </c>
     </row>
@@ -1629,7 +2567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH4"/>
+  <dimension ref="A1:BH8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1650,7 +2588,7 @@
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="21" customWidth="1" min="19" max="19"/>
     <col width="18" customWidth="1" min="20" max="20"/>
     <col width="19" customWidth="1" min="21" max="21"/>
     <col width="16" customWidth="1" min="22" max="22"/>
@@ -2028,32 +2966,32 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I2" t="n">
+        <v>32</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>72.7%</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>20</v>
+      </c>
+      <c r="L2" t="n">
         <v>16</v>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>11</v>
-      </c>
-      <c r="L2" t="n">
-        <v>8</v>
-      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -2065,83 +3003,83 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
+          <t>90.9%</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>9.1%</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>1.454545454545455</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>12</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
           <t>91.7%</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>8.3%</t>
-        </is>
-      </c>
-      <c r="S2" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="V2" t="n">
-        <v>6</v>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
         <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="Y2" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AB2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AE2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>91.7%</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="AE2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="AH2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr"/>
@@ -2149,92 +3087,92 @@
       <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>91.7%</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="AN2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="AQ2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AT2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AV2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AT2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AV2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW2" t="inlineStr">
+      <c r="AX2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BA2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB2" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="AX2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>300.0%</t>
-        </is>
-      </c>
-      <c r="BA2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BC2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>700.0%</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="BC2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BG2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH2" t="inlineStr">
         <is>
           <t>600.0%</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="BG2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>300.0%</t>
         </is>
       </c>
     </row>
@@ -2256,100 +3194,100 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PSC_M._LANDDECK</t>
+          <t>PSC_T._COLEMAN</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>322702</t>
+          <t>322815</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>M. Landdeck</t>
+          <t>T. Coleman</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H3" t="n">
+        <v>9</v>
+      </c>
+      <c r="I3" t="n">
+        <v>19</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>14</v>
+      </c>
+      <c r="L3" t="n">
+        <v>8</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>93.3%</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>6.7%</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>1.266666666666667</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>9</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>55.6%</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
         <v>3</v>
       </c>
-      <c r="I3" t="n">
-        <v>8</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>30.0%</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
-        <v>8</v>
-      </c>
-      <c r="O3" t="n">
-        <v>2</v>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="S3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="V3" t="n">
-        <v>6</v>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="Y3" t="n">
-        <v>2</v>
-      </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -2357,20 +3295,20 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="AE3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr"/>
@@ -2381,33 +3319,33 @@
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="AN3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="AT3" t="n">
@@ -2415,11 +3353,11 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AV3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
@@ -2430,7 +3368,7 @@
         <v>2</v>
       </c>
       <c r="AY3" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
@@ -2438,22 +3376,22 @@
         </is>
       </c>
       <c r="BA3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BD3" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -2488,87 +3426,87 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PSC_L._RAHAMA</t>
+          <t>PSC_P._BASTOS</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>296104</t>
+          <t>155174</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>L. Rahama</t>
+          <t>P. Bastos</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>12</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>0.5833333333333334</v>
+        <v>1.25</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="Y4" t="n">
@@ -2576,33 +3514,33 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="AE4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr"/>
@@ -2613,20 +3551,20 @@
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="AN4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="AQ4" t="n">
@@ -2634,24 +3572,24 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AV4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
@@ -2662,30 +3600,30 @@
         <v>3</v>
       </c>
       <c r="AY4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="BA4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BC4" t="n">
         <v>3</v>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="BA4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>600.0%</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>7</v>
-      </c>
       <c r="BD4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -2698,7 +3636,945 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Portimonense SC</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PSC_J._GREWAL</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>297507</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>J. Grewal</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>17</v>
+      </c>
+      <c r="H5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>13</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>29.4%</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>9</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>8</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>52.9%</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>47.1%</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>0.7647058823529411</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>5</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AT5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AV5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="AX5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="BA5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BC5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BG5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Portimonense SC</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PSC_L._RAHAMA</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>296104</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>L. Rahama</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>7</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>8</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>4</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>6</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
           <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AE6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AT6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AV6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="AX6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BA6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>700.0%</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BG6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Portimonense SC</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PSC_D._FRAGOSO</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>143839</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>D. Fragoso</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>15</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" t="n">
+        <v>8</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>26.7%</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>11</v>
+      </c>
+      <c r="L7" t="n">
+        <v>4</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>4</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>73.3%</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>26.7%</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>0.5333333333333333</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>6</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AE7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AT7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AV7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="AX7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BA7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BC7" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>700.0%</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BG7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Portimonense SC</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PSC_M._LANDDECK</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>322702</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>M. Landdeck</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>26</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>12</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>19.2%</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>10</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>16</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>61.5%</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>0.4615384615384616</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>12</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AN8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AQ8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="AT8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AV8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>700.0%</t>
+        </is>
+      </c>
+      <c r="AX8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BA8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>800.0%</t>
+        </is>
+      </c>
+      <c r="BC8" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>700.0%</t>
+        </is>
+      </c>
+      <c r="BG8" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>500.0%</t>
         </is>
       </c>
     </row>
@@ -2713,7 +4589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH4"/>
+  <dimension ref="A1:BH8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2734,7 +4610,7 @@
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="21" customWidth="1" min="19" max="19"/>
     <col width="18" customWidth="1" min="20" max="20"/>
     <col width="19" customWidth="1" min="21" max="21"/>
     <col width="16" customWidth="1" min="22" max="22"/>
@@ -3112,53 +4988,53 @@
         </is>
       </c>
       <c r="G2" t="n">
+        <v>26</v>
+      </c>
+      <c r="H2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>19.2%</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
         <v>10</v>
       </c>
-      <c r="H2" t="n">
+      <c r="L2" t="n">
         <v>3</v>
       </c>
-      <c r="I2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>30.0%</t>
         </is>
       </c>
-      <c r="K2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
       <c r="N2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O2" t="n">
         <v>2</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>0.8</v>
+        <v>0.4615384615384616</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
@@ -3169,24 +5045,24 @@
         </is>
       </c>
       <c r="V2" t="n">
+        <v>12</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
         <v>6</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="Y2" t="n">
-        <v>2</v>
-      </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -3195,7 +5071,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -3208,16 +5084,26 @@
         </is>
       </c>
       <c r="AE2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
         <v>6</v>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr"/>
@@ -3227,24 +5113,24 @@
         </is>
       </c>
       <c r="AN2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
         <v>6</v>
       </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AQ2" t="n">
-        <v>2</v>
-      </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -3253,7 +5139,7 @@
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -3261,54 +5147,54 @@
         </is>
       </c>
       <c r="AV2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>700.0%</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AY2" t="n">
         <v>1</v>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="BA2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
+          <t>800.0%</t>
+        </is>
+      </c>
+      <c r="BC2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>700.0%</t>
+        </is>
+      </c>
+      <c r="BG2" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
           <t>500.0%</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>400.0%</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>200.0%</t>
-        </is>
-      </c>
-      <c r="BG2" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -3330,87 +5216,87 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PSC_L._RAHAMA</t>
+          <t>PSC_P._BASTOS</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>296104</t>
+          <t>155174</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>L. Rahama</t>
+          <t>P. Bastos</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>12</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>0.5833333333333334</v>
+        <v>1.25</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="Y3" t="n">
@@ -3418,33 +5304,33 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="AE3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr"/>
@@ -3455,20 +5341,20 @@
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="AN3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="AQ3" t="n">
@@ -3476,24 +5362,24 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AV3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
@@ -3504,30 +5390,30 @@
         <v>3</v>
       </c>
       <c r="AY3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="BA3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BC3" t="n">
         <v>3</v>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="BA3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>600.0%</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>7</v>
-      </c>
       <c r="BD3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -3540,7 +5426,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
     </row>
@@ -3562,82 +5448,82 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PSC_G._ROSADO</t>
+          <t>PSC_J._GREWAL</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>322806</t>
+          <t>297507</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>G. Rosado</t>
+          <t>J. Grewal</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="H4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>13</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>29.4%</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
         <v>8</v>
       </c>
-      <c r="I4" t="n">
-        <v>16</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>11</v>
-      </c>
-      <c r="L4" t="n">
-        <v>8</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>72.7%</t>
-        </is>
-      </c>
-      <c r="N4" t="n">
-        <v>1</v>
-      </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>1.333333333333333</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -3646,143 +5532,1071 @@
         </is>
       </c>
       <c r="Y4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE4" t="n">
         <v>5</v>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AB4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AE4" t="n">
-        <v>6</v>
-      </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AH4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AT4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AV4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="AX4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="BA4" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BC4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BG4" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Portimonense SC</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PSC_L._RAHAMA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>296104</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>L. Rahama</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>12</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>7</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>8</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>4</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="AN4" t="n">
+      <c r="V5" t="n">
         <v>6</v>
       </c>
-      <c r="AO4" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AT5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AV5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="AX5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BA5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>700.0%</t>
+        </is>
+      </c>
+      <c r="BC5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BG5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Portimonense SC</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PSC_D._FRAGOSO</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>143839</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>D. Fragoso</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>15</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" t="n">
+        <v>8</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>26.7%</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>11</v>
+      </c>
+      <c r="L6" t="n">
+        <v>4</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>4</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>73.3%</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>26.7%</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>0.5333333333333333</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>6</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AE6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AT6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AV6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="AX6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BA6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>700.0%</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BG6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Portimonense SC</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PSC_G._ROSADO</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>322806</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>G. Rosado</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>22</v>
+      </c>
+      <c r="H7" t="n">
+        <v>16</v>
+      </c>
+      <c r="I7" t="n">
+        <v>32</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>72.7%</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>20</v>
+      </c>
+      <c r="L7" t="n">
+        <v>16</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>2</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>90.9%</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>9.1%</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>1.454545454545455</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>12</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>91.7%</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AE7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>91.7%</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>91.7%</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AT7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AV7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AX7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BA7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="BC7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>700.0%</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="BG7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Portimonense SC</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PSC_T._COLEMAN</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>322815</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>T. Coleman</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>15</v>
+      </c>
+      <c r="H8" t="n">
+        <v>9</v>
+      </c>
+      <c r="I8" t="n">
+        <v>19</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>14</v>
+      </c>
+      <c r="L8" t="n">
+        <v>8</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>93.3%</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>6.7%</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>1.266666666666667</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>9</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>55.6%</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC8" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="AP4" t="inlineStr">
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AE8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>55.6%</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AN8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>55.6%</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
         <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="AQ4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AR4" t="inlineStr">
+      <c r="AQ8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AT8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AV8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="AX8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ8" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AT4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AV4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW4" t="inlineStr">
+      <c r="BA8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="BC8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>9</v>
+      </c>
+      <c r="BE8" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="AX4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>300.0%</t>
-        </is>
-      </c>
-      <c r="BA4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB4" t="inlineStr">
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="BG8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH8" t="inlineStr">
         <is>
           <t>100.0%</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>600.0%</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="BG4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>300.0%</t>
         </is>
       </c>
     </row>
@@ -3797,23 +6611,844 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:BH3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="21" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="19" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
+    <col width="17" customWidth="1" min="24" max="24"/>
+    <col width="16" customWidth="1" min="25" max="25"/>
+    <col width="16" customWidth="1" min="26" max="26"/>
+    <col width="16" customWidth="1" min="27" max="27"/>
+    <col width="16" customWidth="1" min="28" max="28"/>
+    <col width="16" customWidth="1" min="29" max="29"/>
+    <col width="22" customWidth="1" min="30" max="30"/>
+    <col width="26" customWidth="1" min="31" max="31"/>
+    <col width="26" customWidth="1" min="32" max="32"/>
+    <col width="22" customWidth="1" min="33" max="33"/>
+    <col width="26" customWidth="1" min="34" max="34"/>
+    <col width="26" customWidth="1" min="35" max="35"/>
+    <col width="22" customWidth="1" min="36" max="36"/>
+    <col width="26" customWidth="1" min="37" max="37"/>
+    <col width="26" customWidth="1" min="38" max="38"/>
+    <col width="19" customWidth="1" min="39" max="39"/>
+    <col width="20" customWidth="1" min="40" max="40"/>
+    <col width="20" customWidth="1" min="41" max="41"/>
+    <col width="17" customWidth="1" min="42" max="42"/>
+    <col width="20" customWidth="1" min="43" max="43"/>
+    <col width="20" customWidth="1" min="44" max="44"/>
+    <col width="16" customWidth="1" min="45" max="45"/>
+    <col width="20" customWidth="1" min="46" max="46"/>
+    <col width="20" customWidth="1" min="47" max="47"/>
+    <col width="23" customWidth="1" min="48" max="48"/>
+    <col width="18" customWidth="1" min="49" max="49"/>
+    <col width="24" customWidth="1" min="50" max="50"/>
+    <col width="22" customWidth="1" min="51" max="51"/>
+    <col width="19" customWidth="1" min="52" max="52"/>
+    <col width="27" customWidth="1" min="53" max="53"/>
+    <col width="22" customWidth="1" min="54" max="54"/>
+    <col width="28" customWidth="1" min="55" max="55"/>
+    <col width="26" customWidth="1" min="56" max="56"/>
+    <col width="23" customWidth="1" min="57" max="57"/>
+    <col width="28" customWidth="1" min="58" max="58"/>
+    <col width="34" customWidth="1" min="59" max="59"/>
+    <col width="29" customWidth="1" min="60" max="60"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>team_name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>team_code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>team_key</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>global_player_id</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>shot_attempts</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>shot_made</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>points_from_shots</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>fg_pct</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>fg2a</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>fg2m</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>fg2_pct</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>fg3a</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>fg3m</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>fg3_pct</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>two_rate</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>three_rate</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>pts_per_shot</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>eligible_profile</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>top_zone_1</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>top_zone_1_att</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>top_zone_1_pct</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>top_zone_2</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>top_zone_2_att</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>top_zone_2_pct</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>top_zone_3</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>top_zone_3_att</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>top_zone_3_pct</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>top_zone_1_qualified</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>top_zone_1_att_qualified</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>top_zone_1_pct_qualified</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>top_zone_2_qualified</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>top_zone_2_att_qualified</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>top_zone_2_pct_qualified</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>top_zone_3_qualified</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>top_zone_3_att_qualified</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>top_zone_3_pct_qualified</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>top_zone_1_all</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>top_zone_1_att_all</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>top_zone_1_pct_all</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>top_zone_2_all</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>top_zone_2_att_all</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>top_zone_2_pct_all</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>top_zone_3_all</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>top_zone_3_att_all</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>top_zone_3_pct_all</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>team_rank_shot_volume</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>team_rank_fg_pct</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>team_rank_pts_per_shot</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>team_rank_3pt_volume</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>team_rank_3pt_pct</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>team_rank_shot_volume_all</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>team_rank_fg_pct_all</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>team_rank_pts_per_shot_all</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>team_rank_3pt_volume_all</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>team_rank_3pt_pct_all</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>team_rank_fg_pct_qualified</t>
+        </is>
+      </c>
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>team_rank_pts_per_shot_qualified</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>team_rank_3pt_pct_qualified</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
+          <t>Portimonense SC</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PSC_P._BASTOS</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>155174</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>P. Bastos</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>12</v>
+      </c>
+      <c r="H2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>10</v>
+      </c>
+      <c r="O2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>5</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="AT2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AV2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="AX2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="BA2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BC2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="BG2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Portimonense SC</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>PSC_M._LANDDECK</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>322702</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>M. Landdeck</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>26</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>12</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>19.2%</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>61.5%</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>0.4615384615384616</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>12</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="AT3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AV3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>700.0%</t>
+        </is>
+      </c>
+      <c r="AX3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>800.0%</t>
+        </is>
+      </c>
+      <c r="BC3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>700.0%</t>
+        </is>
+      </c>
+      <c r="BG3" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>500.0%</t>
         </is>
       </c>
     </row>
@@ -3839,7 +7474,7 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
@@ -3979,41 +7614,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G2" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.8</v>
+        <v>0.9473684210526315</v>
       </c>
       <c r="J2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -4024,7 +7659,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -4032,7 +7667,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="T2" t="n">
@@ -4040,7 +7675,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
     </row>
@@ -4062,41 +7697,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="E3" t="n">
+        <v>35</v>
+      </c>
+      <c r="F3" t="n">
         <v>20</v>
       </c>
-      <c r="F3" t="n">
-        <v>8</v>
-      </c>
       <c r="G3" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.2</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="J3" t="n">
+        <v>35</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20</v>
+      </c>
+      <c r="L3" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="n">
-        <v>20</v>
-      </c>
-      <c r="M3" t="n">
-        <v>8</v>
-      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="O3" t="n">
@@ -4107,7 +7742,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="R3" t="n">
@@ -4115,7 +7750,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="T3" t="n">
@@ -4123,7 +7758,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -4145,31 +7780,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="F4" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G4" t="n">
+        <v>28</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>43.8%</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="J4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K4" t="n">
         <v>14</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>70.0%</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J4" t="n">
-        <v>10</v>
-      </c>
-      <c r="K4" t="n">
-        <v>7</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -4179,7 +7814,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -4190,7 +7825,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="R4" t="n">
@@ -4198,7 +7833,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="T4" t="n">
@@ -4206,7 +7841,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
     </row>
@@ -4232,27 +7867,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.4</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="J5" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -4262,18 +7897,18 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5" t="n">
         <v>4</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="R5" t="n">
@@ -4281,11 +7916,17 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>400.0%</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4309,7 +7950,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -4332,21 +7973,21 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -4354,15 +7995,21 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>5</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
           <t>500.0%</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4386,21 +8033,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -4409,10 +8056,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -4452,7 +8099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U4"/>
+  <dimension ref="A1:U6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -4463,7 +8110,7 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
@@ -4607,27 +8254,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="F2" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="G2" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.4</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="J2" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="K2" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -4637,14 +8284,14 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="O2" t="n">
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -4652,7 +8299,7 @@
         </is>
       </c>
       <c r="R2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -4660,7 +8307,7 @@
         </is>
       </c>
       <c r="T2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -4690,27 +8337,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G3" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.8</v>
+        <v>0.875</v>
       </c>
       <c r="J3" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -4720,14 +8367,14 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="O3" t="n">
         <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -4735,7 +8382,7 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -4743,7 +8390,7 @@
         </is>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -4769,68 +8416,234 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="J4" t="n">
+        <v>12</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>9.1%</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>4</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>4</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Portimonense SC</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>20</v>
-      </c>
-      <c r="F4" t="n">
-        <v>8</v>
-      </c>
-      <c r="G4" t="n">
-        <v>24</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J4" t="n">
+      <c r="E5" t="n">
+        <v>38</v>
+      </c>
+      <c r="F5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G5" t="n">
+        <v>36</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>31.6%</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.9473684210526315</v>
+      </c>
+      <c r="J5" t="n">
         <v>0</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="n">
-        <v>20</v>
-      </c>
-      <c r="M4" t="n">
-        <v>8</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>29.9%</t>
-        </is>
-      </c>
-      <c r="O4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>200.0%</t>
-        </is>
-      </c>
-      <c r="R4" t="n">
-        <v>2</v>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>200.0%</t>
-        </is>
-      </c>
-      <c r="T4" t="n">
-        <v>2</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>200.0%</t>
+      <c r="L5" t="n">
+        <v>38</v>
+      </c>
+      <c r="M5" t="n">
+        <v>12</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>28.8%</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Portimonense SC</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>11</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>11</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>8.3%</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>5</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>5</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>500.0%</t>
         </is>
       </c>
     </row>
@@ -4845,7 +8658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X6"/>
+  <dimension ref="A1:X10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -5029,31 +8842,31 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J2" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="M2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="N2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -5063,7 +8876,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -5074,23 +8887,23 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
           <t>200.0%</t>
         </is>
       </c>
-      <c r="U2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>200.0%</t>
-        </is>
-      </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -5112,56 +8925,56 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PSC_T._COLEMAN</t>
+          <t>PSC_M._LANDDECK</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>322815</t>
+          <t>322702</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>T. Coleman</t>
+          <t>M. Landdeck</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
         <v>6</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="R3" t="n">
@@ -5210,53 +9023,53 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PSC_M._LANDDECK</t>
+          <t>PSC_T._COLEMAN</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>322702</t>
+          <t>322815</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>M. Landdeck</t>
+          <t>T. Coleman</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="M4" t="n">
+        <v>9</v>
+      </c>
+      <c r="N4" t="n">
+        <v>5</v>
+      </c>
+      <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>0</v>
       </c>
-      <c r="O4" t="n">
-        <v>6</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2</v>
-      </c>
       <c r="Q4" t="inlineStr">
         <is>
           <t>60.0%</t>
@@ -5278,7 +9091,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="W4" t="n">
@@ -5308,17 +9121,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PSC_L._RAHAMA</t>
+          <t>PSC_G._ROSADO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>296104</t>
+          <t>322806</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>L. Rahama</t>
+          <t>G. Rosado</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -5327,27 +9140,27 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.3333333333333333</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="M5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -5357,22 +9170,22 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="R5" t="n">
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -5380,11 +9193,11 @@
         </is>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
     </row>
@@ -5406,17 +9219,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PSC_G._ROSADO</t>
+          <t>PSC_D._FRAGOSO</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>322806</t>
+          <t>143839</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>G. Rosado</t>
+          <t>D. Fragoso</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -5425,27 +9238,27 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="L6" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="M6" t="n">
+        <v>6</v>
+      </c>
+      <c r="N6" t="n">
         <v>2</v>
-      </c>
-      <c r="M6" t="n">
-        <v>5</v>
-      </c>
-      <c r="N6" t="n">
-        <v>5</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -5455,32 +9268,424 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Portimonense SC</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PSC_L._RAHAMA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>296104</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>L. Rahama</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>6</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="M7" t="n">
+        <v>6</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Portimonense SC</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PSC_M._LANDDECK</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>322702</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>M. Landdeck</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="M8" t="n">
+        <v>6</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>23.1%</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>2</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Portimonense SC</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PSC_P._BASTOS</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>155174</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>P. Bastos</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>12</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>5</v>
+      </c>
+      <c r="P9" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>41.7%</t>
         </is>
       </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2</v>
-      </c>
-      <c r="T6" t="inlineStr">
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="U6" t="n">
-        <v>2</v>
-      </c>
-      <c r="V6" t="inlineStr">
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="W6" t="n">
-        <v>2</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W9" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Portimonense SC</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>PSC_J._GREWAL</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>297507</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>J. Grewal</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>5</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>9</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>5</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>29.4%</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="W10" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -5497,23 +9702,448 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:X4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="23" customWidth="1" min="18" max="18"/>
+    <col width="28" customWidth="1" min="19" max="19"/>
+    <col width="25" customWidth="1" min="20" max="20"/>
+    <col width="32" customWidth="1" min="21" max="21"/>
+    <col width="29" customWidth="1" min="22" max="22"/>
+    <col width="38" customWidth="1" min="23" max="23"/>
+    <col width="35" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>team_name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>team_code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>team_key</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>global_player_id</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>zone</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>attempts</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>made</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>fg_pct</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>pps</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>fg2a</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>fg2m</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>fg3a</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>fg3m</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>zone_share</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>eligible_zone_profile</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>player_zone_rank_by_volume</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>player_zone_rank_by_pct</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>player_zone_rank_by_volume_all</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>player_zone_rank_by_pct_all</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>player_zone_rank_by_volume_qualified</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>player_zone_rank_by_pct_qualified</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
+          <t>Portimonense SC</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PSC_G._ROSADO</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>322806</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>G. Rosado</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="n">
+        <v>11</v>
+      </c>
+      <c r="J2" t="n">
+        <v>22</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>91.7%</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="M2" t="n">
+        <v>12</v>
+      </c>
+      <c r="N2" t="n">
+        <v>11</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>54.5%</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Portimonense SC</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>PSC_T._COLEMAN</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>322815</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>T. Coleman</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>9</v>
+      </c>
+      <c r="I3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>10</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>55.6%</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="M3" t="n">
+        <v>9</v>
+      </c>
+      <c r="N3" t="n">
+        <v>5</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Portimonense SC</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PSC_M._LANDDECK</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>322702</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>M. Landdeck</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>6</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>12</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>46.2%</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
         </is>
       </c>
     </row>

--- a/site/leagues/betclic/2026_2027/xlsx/opponent_shooting_packs/opponent_shooting_pack_PSC.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/opponent_shooting_packs/opponent_shooting_pack_PSC.xlsx
@@ -425,7 +425,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -482,7 +482,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M. Landdeck (26 L)</t>
+          <t>M. Landdeck (43 L)</t>
         </is>
       </c>
     </row>
@@ -494,7 +494,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M. Landdeck (16.0 3PA)</t>
+          <t>M. Landdeck (26.0 3PA)</t>
         </is>
       </c>
     </row>
@@ -506,7 +506,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>G. Rosado (1.455)</t>
+          <t>G. Rosado (1.517)</t>
         </is>
       </c>
     </row>
@@ -518,7 +518,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Above the Break 3 (38 L)</t>
+          <t>Paint Non-RA (58 L)</t>
         </is>
       </c>
     </row>
@@ -530,7 +530,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Restricted Area (57.1%)</t>
+          <t>Restricted Area (60.0%)</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH8"/>
+  <dimension ref="A1:BH9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -566,7 +566,7 @@
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="21" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
     <col width="18" customWidth="1" min="20" max="20"/>
     <col width="19" customWidth="1" min="21" max="21"/>
     <col width="16" customWidth="1" min="22" max="22"/>
@@ -944,53 +944,53 @@
         </is>
       </c>
       <c r="G2" t="n">
+        <v>43</v>
+      </c>
+      <c r="H2" t="n">
+        <v>14</v>
+      </c>
+      <c r="I2" t="n">
+        <v>35</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>32.6%</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>17</v>
+      </c>
+      <c r="L2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>41.2%</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
         <v>26</v>
       </c>
-      <c r="H2" t="n">
-        <v>5</v>
-      </c>
-      <c r="I2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>19.2%</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>10</v>
-      </c>
-      <c r="L2" t="n">
-        <v>3</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>30.0%</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>16</v>
-      </c>
       <c r="O2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.813953488372093</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
@@ -1001,16 +1001,16 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="Y2" t="n">
@@ -1018,38 +1018,38 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
           <t>16.7%</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="AB2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="AD2" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
       <c r="AE2" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="AH2" t="n">
@@ -1057,28 +1057,38 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AK2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
           <t>16.7%</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
       <c r="AN2" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="AQ2" t="n">
@@ -1086,71 +1096,71 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AT2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>16.7%</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="AT2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="AV2" t="n">
         <v>1</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>700.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY2" t="n">
         <v>1</v>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BA2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BC2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
           <t>500.0%</t>
         </is>
       </c>
-      <c r="BA2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>800.0%</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BG2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH2" t="inlineStr">
         <is>
           <t>600.0%</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>700.0%</t>
-        </is>
-      </c>
-      <c r="BG2" t="n">
-        <v>7</v>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>500.0%</t>
         </is>
       </c>
     </row>
@@ -1186,28 +1196,28 @@
         </is>
       </c>
       <c r="G3" t="n">
+        <v>29</v>
+      </c>
+      <c r="H3" t="n">
         <v>22</v>
       </c>
-      <c r="H3" t="n">
-        <v>16</v>
-      </c>
       <c r="I3" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>75.9%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="L3" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -1223,16 +1233,16 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>93.1%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>1.454545454545455</v>
+        <v>1.517241379310345</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -1243,11 +1253,11 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1256,11 +1266,11 @@
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -1282,11 +1292,11 @@
         </is>
       </c>
       <c r="AE3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1295,11 +1305,11 @@
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr"/>
@@ -1311,11 +1321,11 @@
         </is>
       </c>
       <c r="AN3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -1324,11 +1334,11 @@
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1360,7 +1370,7 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>600.0%</t>
+          <t>700.0%</t>
         </is>
       </c>
       <c r="BA3" t="n">
@@ -1379,20 +1389,20 @@
       </c>
       <c r="BE3" t="inlineStr">
         <is>
+          <t>800.0%</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="BG3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
           <t>700.0%</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="BG3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>600.0%</t>
         </is>
       </c>
     </row>
@@ -1414,82 +1424,82 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PSC_J._GREWAL</t>
+          <t>PSC_T._COLEMAN</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>297507</t>
+          <t>322815</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>J. Grewal</t>
+          <t>T. Coleman</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I4" t="n">
+        <v>29</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>56.0%</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>24</v>
+      </c>
+      <c r="L4" t="n">
         <v>13</v>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>29.4%</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>9</v>
-      </c>
-      <c r="L4" t="n">
-        <v>2</v>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>96.0%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>0.7647058823529411</v>
+        <v>1.16</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1498,11 +1508,11 @@
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1520,34 +1530,44 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="AE4" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
+          <t>53.3%</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="AN4" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1556,11 +1576,11 @@
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1581,18 +1601,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="BA4" t="n">
@@ -1600,31 +1620,31 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BD4" t="n">
+        <v>9</v>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="BG4" t="n">
         <v>3</v>
       </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>300.0%</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>400.0%</t>
-        </is>
-      </c>
-      <c r="BG4" t="n">
-        <v>4</v>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -1646,121 +1666,121 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PSC_T._COLEMAN</t>
+          <t>PSC_J._GREWAL</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>322815</t>
+          <t>297507</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>T. Coleman</t>
+          <t>J. Grewal</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I5" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="L5" t="n">
+        <v>4</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>11</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>27.3%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>0.7727272727272727</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
         <v>8</v>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>57.1%</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>93.3%</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>6.7%</t>
-        </is>
-      </c>
-      <c r="S5" t="n">
-        <v>1.266666666666667</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="V5" t="n">
-        <v>9</v>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>55.6%</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="Y5" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
       <c r="AB5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="AE5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr"/>
@@ -1771,41 +1791,41 @@
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="AN5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>55.6%</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
+      <c r="AQ5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
         <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="AQ5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
       <c r="AT5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="AV5" t="n">
@@ -1813,18 +1833,18 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
       <c r="AX5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY5" t="n">
         <v>2</v>
       </c>
-      <c r="AY5" t="n">
-        <v>9</v>
-      </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="BA5" t="n">
@@ -1832,31 +1852,31 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>700.0%</t>
         </is>
       </c>
       <c r="BC5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD5" t="n">
         <v>2</v>
       </c>
-      <c r="BD5" t="n">
-        <v>9</v>
-      </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
       <c r="BG5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
     </row>
@@ -1878,87 +1898,87 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PSC_D._FRAGOSO</t>
+          <t>PSC_L._RAHAMA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>143839</t>
+          <t>296104</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>D. Fragoso</t>
+          <t>L. Rahama</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I6" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L6" t="n">
         <v>4</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.7</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="Y6" t="n">
@@ -1966,12 +1986,12 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="AB6" t="n">
@@ -1979,20 +1999,20 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="AE6" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr"/>
@@ -2003,20 +2023,20 @@
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="AN6" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="AQ6" t="n">
@@ -2024,12 +2044,12 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="AT6" t="n">
@@ -2037,58 +2057,58 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AV6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>800.0%</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>600.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="BA6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>600.0%</t>
+          <t>900.0%</t>
         </is>
       </c>
       <c r="BC6" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>800.0%</t>
+        </is>
+      </c>
+      <c r="BG6" t="n">
         <v>7</v>
       </c>
-      <c r="BD6" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>700.0%</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>500.0%</t>
-        </is>
-      </c>
-      <c r="BG6" t="n">
-        <v>6</v>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>600.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
     </row>
@@ -2110,121 +2130,121 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>PSC_P._BASTOS</t>
+          <t>PSC_D._FRAGOSO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>155174</t>
+          <t>143839</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>P. Bastos</t>
+          <t>D. Fragoso</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H7" t="n">
         <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>31.2%</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>12</v>
+      </c>
+      <c r="L7" t="n">
+        <v>5</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
           <t>41.7%</t>
         </is>
       </c>
-      <c r="K7" t="n">
-        <v>2</v>
-      </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
+        <v>4</v>
+      </c>
+      <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="N7" t="n">
-        <v>10</v>
-      </c>
-      <c r="O7" t="n">
-        <v>5</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>1.25</v>
+        <v>0.625</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>6</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="V7" t="n">
-        <v>5</v>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="Y7" t="n">
+      <c r="AB7" t="n">
         <v>3</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="AE7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr"/>
@@ -2235,41 +2255,41 @@
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="AN7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="AQ7" t="n">
+      <c r="AT7" t="n">
         <v>3</v>
       </c>
-      <c r="AR7" t="inlineStr">
+      <c r="AU7" t="inlineStr">
         <is>
           <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
-      <c r="AT7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>50.0%</t>
         </is>
       </c>
       <c r="AV7" t="n">
@@ -2277,18 +2297,18 @@
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>700.0%</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AY7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>700.0%</t>
         </is>
       </c>
       <c r="BA7" t="n">
@@ -2296,31 +2316,31 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>800.0%</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="BD7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>800.0%</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>700.0%</t>
         </is>
       </c>
       <c r="BG7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>700.0%</t>
         </is>
       </c>
     </row>
@@ -2342,74 +2362,74 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PSC_L._RAHAMA</t>
+          <t>PSC_P._BASTOS</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>296104</t>
+          <t>155174</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>L. Rahama</t>
+          <t>P. Bastos</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>84.6%</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>0.5833333333333334</v>
+        <v>1.153846153846154</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="V8" t="n">
@@ -2417,12 +2437,12 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="Y8" t="n">
@@ -2430,25 +2450,25 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="AE8" t="n">
@@ -2456,7 +2476,7 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr"/>
@@ -2467,7 +2487,7 @@
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="AN8" t="n">
@@ -2475,12 +2495,12 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="AQ8" t="n">
@@ -2488,71 +2508,303 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AV8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>600.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="AX8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="BA8" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BC8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BG8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Portimonense SC</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PSC_P._OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>169338</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>P. Oliveira</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>12</v>
+      </c>
+      <c r="H9" t="n">
+        <v>7</v>
+      </c>
+      <c r="I9" t="n">
+        <v>17</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>58.3%</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
         <v>5</v>
       </c>
-      <c r="AY8" t="n">
+      <c r="L9" t="n">
         <v>4</v>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>400.0%</t>
-        </is>
-      </c>
-      <c r="BA8" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>700.0%</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD8" t="n">
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>7</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>58.3%</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>1.416666666666667</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>5</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AN9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="AT9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AV9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="AX9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY9" t="n">
         <v>4</v>
       </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>400.0%</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>600.0%</t>
-        </is>
-      </c>
-      <c r="BG8" t="n">
-        <v>5</v>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>400.0%</t>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="BA9" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="BC9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="BG9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>300.0%</t>
         </is>
       </c>
     </row>
@@ -2567,7 +2819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH8"/>
+  <dimension ref="A1:BH9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2588,7 +2840,7 @@
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="21" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
     <col width="18" customWidth="1" min="20" max="20"/>
     <col width="19" customWidth="1" min="21" max="21"/>
     <col width="16" customWidth="1" min="22" max="22"/>
@@ -2966,28 +3218,28 @@
         </is>
       </c>
       <c r="G2" t="n">
+        <v>29</v>
+      </c>
+      <c r="H2" t="n">
         <v>22</v>
       </c>
-      <c r="H2" t="n">
-        <v>16</v>
-      </c>
       <c r="I2" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>75.9%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="L2" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -3003,16 +3255,16 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>93.1%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>1.454545454545455</v>
+        <v>1.517241379310345</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
@@ -3023,11 +3275,11 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -3036,11 +3288,11 @@
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -3062,11 +3314,11 @@
         </is>
       </c>
       <c r="AE2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -3075,11 +3327,11 @@
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr"/>
@@ -3091,11 +3343,11 @@
         </is>
       </c>
       <c r="AN2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -3104,11 +3356,11 @@
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -3140,7 +3392,7 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>600.0%</t>
+          <t>700.0%</t>
         </is>
       </c>
       <c r="BA2" t="n">
@@ -3159,20 +3411,20 @@
       </c>
       <c r="BE2" t="inlineStr">
         <is>
+          <t>800.0%</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="BG2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
           <t>700.0%</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="BG2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>600.0%</t>
         </is>
       </c>
     </row>
@@ -3194,87 +3446,87 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PSC_T._COLEMAN</t>
+          <t>PSC_P._OLIVEIRA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>322815</t>
+          <t>169338</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>T. Coleman</t>
+          <t>P. Oliveira</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="L3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>93.3%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>1.266666666666667</v>
+        <v>1.416666666666667</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>5</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="V3" t="n">
-        <v>9</v>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>55.6%</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
         </is>
       </c>
       <c r="Y3" t="n">
@@ -3287,7 +3539,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -3300,15 +3552,15 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="AE3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr"/>
@@ -3319,20 +3571,20 @@
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AN3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>55.6%</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
         </is>
       </c>
       <c r="AQ3" t="n">
@@ -3345,7 +3597,7 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="AT3" t="n">
@@ -3357,7 +3609,7 @@
         </is>
       </c>
       <c r="AV3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
@@ -3368,15 +3620,15 @@
         <v>2</v>
       </c>
       <c r="AY3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="BA3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
@@ -3387,11 +3639,11 @@
         <v>2</v>
       </c>
       <c r="BD3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -3404,7 +3656,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
     </row>
@@ -3426,170 +3678,180 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PSC_P._BASTOS</t>
+          <t>PSC_T._COLEMAN</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>155174</t>
+          <t>322815</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>P. Bastos</t>
+          <t>T. Coleman</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I4" t="n">
+        <v>29</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>56.0%</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>24</v>
+      </c>
+      <c r="L4" t="n">
+        <v>13</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>54.2%</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>96.0%</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
         <v>15</v>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>41.7%</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="N4" t="n">
-        <v>10</v>
-      </c>
-      <c r="O4" t="n">
-        <v>5</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>83.3%</t>
-        </is>
-      </c>
-      <c r="S4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="V4" t="n">
-        <v>5</v>
-      </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="Y4" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
         <v>3</v>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
-      <c r="AB4" t="n">
-        <v>2</v>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="AE4" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
+          <t>53.3%</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="AN4" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="AQ4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AT4" t="n">
         <v>3</v>
       </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
-      <c r="AT4" t="n">
-        <v>2</v>
-      </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AV4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
@@ -3600,30 +3862,30 @@
         <v>3</v>
       </c>
       <c r="AY4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="BA4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="BC4" t="n">
         <v>3</v>
       </c>
       <c r="BD4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -3636,7 +3898,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -3658,121 +3920,121 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PSC_J._GREWAL</t>
+          <t>PSC_P._BASTOS</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>297507</t>
+          <t>155174</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>J. Grewal</t>
+          <t>P. Bastos</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H5" t="n">
         <v>5</v>
       </c>
       <c r="I5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>11</v>
+      </c>
+      <c r="O5" t="n">
+        <v>5</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>45.5%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>15.4%</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>84.6%</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>1.153846153846154</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>6</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
         <v>2</v>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>22.2%</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
-        <v>8</v>
-      </c>
-      <c r="O5" t="n">
-        <v>3</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>37.5%</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>52.9%</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>47.1%</t>
-        </is>
-      </c>
-      <c r="S5" t="n">
-        <v>0.7647058823529411</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="V5" t="n">
-        <v>5</v>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="Y5" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
       <c r="AE5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr"/>
@@ -3787,41 +4049,41 @@
         </is>
       </c>
       <c r="AN5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AV5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
@@ -3832,30 +4094,30 @@
         <v>4</v>
       </c>
       <c r="AY5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="BA5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BD5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
@@ -3868,7 +4130,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
     </row>
@@ -3890,209 +4152,229 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PSC_L._RAHAMA</t>
+          <t>PSC_M._LANDDECK</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>296104</t>
+          <t>322702</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>L. Rahama</t>
+          <t>M. Landdeck</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="I6" t="n">
+        <v>35</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>32.6%</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>17</v>
+      </c>
+      <c r="L6" t="n">
         <v>7</v>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>8</v>
-      </c>
-      <c r="L6" t="n">
-        <v>2</v>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
+          <t>60.5%</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>0.813953488372093</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>21</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
           <t>33.3%</t>
         </is>
       </c>
-      <c r="S6" t="n">
-        <v>0.5833333333333334</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="V6" t="n">
+      <c r="Y6" t="n">
         <v>6</v>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC6" t="inlineStr">
         <is>
           <t>16.7%</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="Y6" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AE6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF6" t="inlineStr">
         <is>
           <t>33.3%</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
         <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="AB6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AK6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
         <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="AE6" t="n">
+      <c r="AQ6" t="n">
         <v>6</v>
       </c>
-      <c r="AF6" t="inlineStr">
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AT6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU6" t="inlineStr">
         <is>
           <t>16.7%</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AN6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AQ6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AT6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
       <c r="AV6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>600.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="AX6" t="n">
         <v>5</v>
       </c>
       <c r="AY6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
       <c r="BA6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>700.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
       <c r="BC6" t="n">
         <v>6</v>
       </c>
       <c r="BD6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>600.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="BG6" t="n">
@@ -4100,7 +4382,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
     </row>
@@ -4122,31 +4404,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>PSC_D._FRAGOSO</t>
+          <t>PSC_J._GREWAL</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>143839</t>
+          <t>297507</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>D. Fragoso</t>
+          <t>J. Grewal</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I7" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -4161,82 +4443,82 @@
         </is>
       </c>
       <c r="N7" t="n">
+        <v>11</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>27.3%</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>0.7727272727272727</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>8</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
         <v>4</v>
       </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>73.3%</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>26.7%</t>
-        </is>
-      </c>
-      <c r="S7" t="n">
-        <v>0.5333333333333333</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="V7" t="n">
-        <v>6</v>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="Y7" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="AB7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="AE7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr"/>
@@ -4247,41 +4529,41 @@
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="AN7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AQ7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
       <c r="AT7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="AV7" t="n">
@@ -4289,18 +4571,18 @@
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
       <c r="AX7" t="n">
         <v>6</v>
       </c>
       <c r="AY7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>600.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="BA7" t="n">
@@ -4308,23 +4590,23 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>600.0%</t>
+          <t>700.0%</t>
         </is>
       </c>
       <c r="BC7" t="n">
         <v>7</v>
       </c>
       <c r="BD7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>700.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
       <c r="BG7" t="n">
@@ -4332,7 +4614,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>600.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
     </row>
@@ -4354,95 +4636,95 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PSC_M._LANDDECK</t>
+          <t>PSC_L._RAHAMA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>322702</t>
+          <t>296104</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>M. Landdeck</t>
+          <t>L. Rahama</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="O8" t="n">
         <v>2</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.7</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>11</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>18.2%</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="V8" t="n">
-        <v>12</v>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="Y8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -4455,62 +4737,52 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="AE8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AH8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
+          <t>18.2%</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="inlineStr"/>
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AN8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>18.2%</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="AN8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="AQ8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -4523,50 +4795,50 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AV8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>700.0%</t>
+          <t>800.0%</t>
         </is>
       </c>
       <c r="AX8" t="n">
         <v>7</v>
       </c>
       <c r="AY8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="BA8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>800.0%</t>
+          <t>900.0%</t>
         </is>
       </c>
       <c r="BC8" t="n">
         <v>8</v>
       </c>
       <c r="BD8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>600.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>700.0%</t>
+          <t>800.0%</t>
         </is>
       </c>
       <c r="BG8" t="n">
@@ -4574,7 +4846,239 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>400.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Portimonense SC</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PSC_D._FRAGOSO</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>143839</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>D. Fragoso</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>16</v>
+      </c>
+      <c r="H9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>10</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>31.2%</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>12</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>4</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>6</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AE9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AN9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AT9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AV9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>700.0%</t>
+        </is>
+      </c>
+      <c r="AX9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>700.0%</t>
+        </is>
+      </c>
+      <c r="BA9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>800.0%</t>
+        </is>
+      </c>
+      <c r="BC9" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>800.0%</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>700.0%</t>
+        </is>
+      </c>
+      <c r="BG9" t="n">
+        <v>8</v>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>700.0%</t>
         </is>
       </c>
     </row>
@@ -4589,7 +5093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH8"/>
+  <dimension ref="A1:BH9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -4610,7 +5114,7 @@
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="21" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
     <col width="18" customWidth="1" min="20" max="20"/>
     <col width="19" customWidth="1" min="21" max="21"/>
     <col width="16" customWidth="1" min="22" max="22"/>
@@ -4988,53 +5492,53 @@
         </is>
       </c>
       <c r="G2" t="n">
+        <v>43</v>
+      </c>
+      <c r="H2" t="n">
+        <v>14</v>
+      </c>
+      <c r="I2" t="n">
+        <v>35</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>32.6%</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>17</v>
+      </c>
+      <c r="L2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>41.2%</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
         <v>26</v>
       </c>
-      <c r="H2" t="n">
-        <v>5</v>
-      </c>
-      <c r="I2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>19.2%</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>10</v>
-      </c>
-      <c r="L2" t="n">
-        <v>3</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>30.0%</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>16</v>
-      </c>
       <c r="O2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.813953488372093</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
@@ -5045,16 +5549,16 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="Y2" t="n">
@@ -5062,38 +5566,38 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
           <t>16.7%</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="AB2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="AD2" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
       <c r="AE2" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="AH2" t="n">
@@ -5101,28 +5605,38 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AK2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
           <t>16.7%</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
       <c r="AN2" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="AQ2" t="n">
@@ -5130,71 +5644,71 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AT2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>16.7%</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="AT2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="AV2" t="n">
         <v>1</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>700.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY2" t="n">
         <v>1</v>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BA2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BC2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
           <t>500.0%</t>
         </is>
       </c>
-      <c r="BA2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>800.0%</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BG2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH2" t="inlineStr">
         <is>
           <t>600.0%</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>700.0%</t>
-        </is>
-      </c>
-      <c r="BG2" t="n">
-        <v>7</v>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>500.0%</t>
         </is>
       </c>
     </row>
@@ -5230,7 +5744,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H3" t="n">
         <v>5</v>
@@ -5240,7 +5754,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -5255,28 +5769,28 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O3" t="n">
         <v>5</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>84.6%</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>1.25</v>
+        <v>1.153846153846154</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -5287,11 +5801,11 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -5326,11 +5840,11 @@
         </is>
       </c>
       <c r="AE3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr"/>
@@ -5345,11 +5859,11 @@
         </is>
       </c>
       <c r="AN3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -5379,15 +5893,15 @@
         </is>
       </c>
       <c r="AV3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY3" t="n">
         <v>2</v>
@@ -5398,7 +5912,7 @@
         </is>
       </c>
       <c r="BA3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
@@ -5406,7 +5920,7 @@
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BD3" t="n">
         <v>2</v>
@@ -5418,11 +5932,11 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="BG3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
@@ -5462,73 +5976,73 @@
         </is>
       </c>
       <c r="G4" t="n">
+        <v>22</v>
+      </c>
+      <c r="H4" t="n">
+        <v>7</v>
+      </c>
+      <c r="I4" t="n">
         <v>17</v>
       </c>
-      <c r="H4" t="n">
-        <v>5</v>
-      </c>
-      <c r="I4" t="n">
-        <v>13</v>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>27.3%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>0.7727272727272727</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
           <t>37.5%</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>52.9%</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>47.1%</t>
-        </is>
-      </c>
-      <c r="S4" t="n">
-        <v>0.7647058823529411</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="V4" t="n">
-        <v>5</v>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="Y4" t="n">
@@ -5536,33 +6050,33 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
           <t>25.0%</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="AB4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
       <c r="AD4" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
       <c r="AE4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr"/>
@@ -5577,16 +6091,16 @@
         </is>
       </c>
       <c r="AN4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="AQ4" t="n">
@@ -5594,71 +6108,71 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AT4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>25.0%</t>
         </is>
       </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="AT4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
       <c r="AV4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
       <c r="AX4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BA4" t="n">
         <v>4</v>
       </c>
-      <c r="AY4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>300.0%</t>
-        </is>
-      </c>
-      <c r="BA4" t="n">
-        <v>3</v>
-      </c>
       <c r="BB4" t="inlineStr">
         <is>
+          <t>700.0%</t>
+        </is>
+      </c>
+      <c r="BC4" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
           <t>500.0%</t>
         </is>
       </c>
-      <c r="BC4" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>3</v>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>300.0%</t>
-        </is>
-      </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
       <c r="BG4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
     </row>
@@ -5680,87 +6194,87 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PSC_L._RAHAMA</t>
+          <t>PSC_P._OLIVEIRA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>296104</t>
+          <t>169338</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>L. Rahama</t>
+          <t>P. Oliveira</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>12</v>
       </c>
       <c r="H5" t="n">
+        <v>7</v>
+      </c>
+      <c r="I5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>58.3%</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>5</v>
+      </c>
+      <c r="L5" t="n">
+        <v>4</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>7</v>
+      </c>
+      <c r="O5" t="n">
         <v>3</v>
       </c>
-      <c r="I5" t="n">
-        <v>7</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>8</v>
-      </c>
-      <c r="L5" t="n">
-        <v>2</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
-        <v>4</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1</v>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>0.5833333333333334</v>
+        <v>1.416666666666667</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>5</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="V5" t="n">
-        <v>6</v>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="Y5" t="n">
@@ -5768,33 +6282,33 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="AE5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr"/>
@@ -5805,20 +6319,20 @@
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AN5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="AQ5" t="n">
@@ -5826,71 +6340,71 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AV5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>600.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AY5" t="n">
         <v>4</v>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="BA5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>700.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BD5" t="n">
         <v>4</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>600.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="BG5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
     </row>
@@ -5912,87 +6426,87 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PSC_D._FRAGOSO</t>
+          <t>PSC_L._RAHAMA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>143839</t>
+          <t>296104</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>D. Fragoso</t>
+          <t>L. Rahama</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I6" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L6" t="n">
         <v>4</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.7</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="Y6" t="n">
@@ -6000,12 +6514,12 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="AB6" t="n">
@@ -6013,20 +6527,20 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="AE6" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr"/>
@@ -6037,20 +6551,20 @@
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="AN6" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="AQ6" t="n">
@@ -6058,12 +6572,12 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="AT6" t="n">
@@ -6071,58 +6585,58 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AV6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>800.0%</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>600.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="BA6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>600.0%</t>
+          <t>900.0%</t>
         </is>
       </c>
       <c r="BC6" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>800.0%</t>
+        </is>
+      </c>
+      <c r="BG6" t="n">
         <v>7</v>
       </c>
-      <c r="BD6" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>700.0%</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>500.0%</t>
-        </is>
-      </c>
-      <c r="BG6" t="n">
-        <v>6</v>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>600.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
     </row>
@@ -6144,46 +6658,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>PSC_G._ROSADO</t>
+          <t>PSC_D._FRAGOSO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>322806</t>
+          <t>143839</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>G. Rosado</t>
+          <t>D. Fragoso</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H7" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="L7" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -6195,16 +6709,16 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>1.454545454545455</v>
+        <v>0.625</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
@@ -6215,11 +6729,11 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -6228,11 +6742,11 @@
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -6241,7 +6755,7 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
@@ -6254,26 +6768,16 @@
         </is>
       </c>
       <c r="AE7" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>91.7%</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AH7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>57.1%</t>
-        </is>
-      </c>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="inlineStr"/>
@@ -6283,11 +6787,11 @@
         </is>
       </c>
       <c r="AN7" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
@@ -6296,75 +6800,75 @@
         </is>
       </c>
       <c r="AQ7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AT7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AV7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>700.0%</t>
+        </is>
+      </c>
+      <c r="AX7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY7" t="n">
         <v>7</v>
       </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>57.1%</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AT7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AV7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AX7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY7" t="n">
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>700.0%</t>
+        </is>
+      </c>
+      <c r="BA7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>800.0%</t>
+        </is>
+      </c>
+      <c r="BC7" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>800.0%</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>700.0%</t>
+        </is>
+      </c>
+      <c r="BG7" t="n">
         <v>8</v>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>600.0%</t>
-        </is>
-      </c>
-      <c r="BA7" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="BC7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>8</v>
-      </c>
-      <c r="BE7" t="inlineStr">
+      <c r="BH7" t="inlineStr">
         <is>
           <t>700.0%</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="BG7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>600.0%</t>
         </is>
       </c>
     </row>
@@ -6386,100 +6890,100 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PSC_T._COLEMAN</t>
+          <t>PSC_G._ROSADO</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>322815</t>
+          <t>322806</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>T. Coleman</t>
+          <t>G. Rosado</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="H8" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="I8" t="n">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>75.9%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="L8" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>93.3%</t>
+          <t>93.1%</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>1.266666666666667</v>
+        <v>1.517241379310345</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>13</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>92.3%</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="V8" t="n">
-        <v>9</v>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>55.6%</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="Y8" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="AB8" t="n">
@@ -6487,57 +6991,67 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AE8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>92.3%</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="AE8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>55.6%</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
+      <c r="AH8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>69.2%</t>
+        </is>
+      </c>
       <c r="AJ8" t="inlineStr"/>
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AN8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>92.3%</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="AN8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>55.6%</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="AQ8" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="AT8" t="n">
@@ -6545,56 +7059,298 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AV8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="AX8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>700.0%</t>
+        </is>
+      </c>
+      <c r="BA8" t="n">
         <v>2</v>
       </c>
-      <c r="AY8" t="n">
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="BC8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>800.0%</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="BG8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>700.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Portimonense SC</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PSC_T._COLEMAN</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>322815</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>T. Coleman</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>25</v>
+      </c>
+      <c r="H9" t="n">
+        <v>14</v>
+      </c>
+      <c r="I9" t="n">
+        <v>29</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>56.0%</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>24</v>
+      </c>
+      <c r="L9" t="n">
+        <v>13</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>54.2%</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>96.0%</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>15</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>53.3%</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AE9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>53.3%</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AN9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>53.3%</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AQ9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AT9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AV9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="AX9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY9" t="n">
         <v>9</v>
       </c>
-      <c r="AZ8" t="inlineStr">
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="BA8" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>200.0%</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD8" t="n">
+      <c r="BA9" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="BC9" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD9" t="n">
         <v>9</v>
       </c>
-      <c r="BE8" t="inlineStr">
+      <c r="BE9" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>200.0%</t>
-        </is>
-      </c>
-      <c r="BG8" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH8" t="inlineStr">
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="BG9" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH9" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -6611,7 +7367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH3"/>
+  <dimension ref="A1:BH4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -6632,15 +7388,15 @@
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="21" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
     <col width="18" customWidth="1" min="20" max="20"/>
     <col width="19" customWidth="1" min="21" max="21"/>
     <col width="16" customWidth="1" min="22" max="22"/>
     <col width="16" customWidth="1" min="23" max="23"/>
-    <col width="17" customWidth="1" min="24" max="24"/>
+    <col width="15" customWidth="1" min="24" max="24"/>
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
-    <col width="16" customWidth="1" min="27" max="27"/>
+    <col width="17" customWidth="1" min="27" max="27"/>
     <col width="16" customWidth="1" min="28" max="28"/>
     <col width="16" customWidth="1" min="29" max="29"/>
     <col width="22" customWidth="1" min="30" max="30"/>
@@ -6655,10 +7411,10 @@
     <col width="19" customWidth="1" min="39" max="39"/>
     <col width="20" customWidth="1" min="40" max="40"/>
     <col width="20" customWidth="1" min="41" max="41"/>
-    <col width="17" customWidth="1" min="42" max="42"/>
+    <col width="16" customWidth="1" min="42" max="42"/>
     <col width="20" customWidth="1" min="43" max="43"/>
     <col width="20" customWidth="1" min="44" max="44"/>
-    <col width="16" customWidth="1" min="45" max="45"/>
+    <col width="17" customWidth="1" min="45" max="45"/>
     <col width="20" customWidth="1" min="46" max="46"/>
     <col width="20" customWidth="1" min="47" max="47"/>
     <col width="23" customWidth="1" min="48" max="48"/>
@@ -7010,7 +7766,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H2" t="n">
         <v>5</v>
@@ -7020,7 +7776,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -7035,28 +7791,28 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O2" t="n">
         <v>5</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>84.6%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>1.25</v>
+        <v>1.153846153846154</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
@@ -7067,11 +7823,11 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -7106,11 +7862,11 @@
         </is>
       </c>
       <c r="AE2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr"/>
@@ -7125,11 +7881,11 @@
         </is>
       </c>
       <c r="AN2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -7159,15 +7915,15 @@
         </is>
       </c>
       <c r="AV2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY2" t="n">
         <v>2</v>
@@ -7178,7 +7934,7 @@
         </is>
       </c>
       <c r="BA2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
@@ -7186,7 +7942,7 @@
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BD2" t="n">
         <v>2</v>
@@ -7198,11 +7954,11 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="BG2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
@@ -7228,67 +7984,67 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PSC_M._LANDDECK</t>
+          <t>PSC_J._GREWAL</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>322702</t>
+          <t>297507</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>M. Landdeck</t>
+          <t>J. Grewal</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L3" t="n">
+        <v>4</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>11</v>
+      </c>
+      <c r="O3" t="n">
         <v>3</v>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>30.0%</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O3" t="n">
-        <v>2</v>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.7727272727272727</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -7299,37 +8055,37 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="Y3" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
       <c r="AB3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -7338,26 +8094,16 @@
         </is>
       </c>
       <c r="AE3" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AH3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr"/>
@@ -7367,88 +8113,340 @@
         </is>
       </c>
       <c r="AN3" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AT3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AV3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="AX3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BA3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>700.0%</t>
+        </is>
+      </c>
+      <c r="BC3" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BG3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Portimonense SC</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PSC_M._LANDDECK</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>322702</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>M. Landdeck</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>43</v>
+      </c>
+      <c r="H4" t="n">
+        <v>14</v>
+      </c>
+      <c r="I4" t="n">
+        <v>35</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>32.6%</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>17</v>
+      </c>
+      <c r="L4" t="n">
+        <v>7</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>41.2%</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>26</v>
+      </c>
+      <c r="O4" t="n">
+        <v>7</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>26.9%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>39.5%</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>60.5%</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>0.813953488372093</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>21</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
           <t>16.7%</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr">
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AK4" t="n">
         <v>6</v>
       </c>
-      <c r="AR3" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>16.7%</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="AT3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AV3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>700.0%</t>
-        </is>
-      </c>
-      <c r="AX3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ3" t="inlineStr">
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AT4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="AV4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW4" t="inlineStr">
         <is>
           <t>500.0%</t>
         </is>
       </c>
-      <c r="BA3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>800.0%</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BE3" t="inlineStr">
+      <c r="AX4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>600.0%</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>700.0%</t>
-        </is>
-      </c>
-      <c r="BG3" t="n">
-        <v>7</v>
-      </c>
-      <c r="BH3" t="inlineStr">
+      <c r="BA4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BC4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
         <is>
           <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BG4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>600.0%</t>
         </is>
       </c>
     </row>
@@ -7614,41 +8612,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="F2" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="G2" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.9473684210526315</v>
+        <v>1.03448275862069</v>
       </c>
       <c r="J2" t="n">
+        <v>58</v>
+      </c>
+      <c r="K2" t="n">
+        <v>30</v>
+      </c>
+      <c r="L2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="n">
-        <v>38</v>
-      </c>
-      <c r="M2" t="n">
-        <v>12</v>
-      </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -7659,7 +8657,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -7667,7 +8665,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="T2" t="n">
@@ -7675,7 +8673,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
     </row>
@@ -7697,41 +8695,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="F3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G3" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.142857142857143</v>
+        <v>1.075471698113208</v>
       </c>
       <c r="J3" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="O3" t="n">
@@ -7742,7 +8740,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="R3" t="n">
@@ -7750,7 +8748,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="T3" t="n">
@@ -7758,7 +8756,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
     </row>
@@ -7780,31 +8778,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F4" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="G4" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.875</v>
+        <v>1.2</v>
       </c>
       <c r="J4" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="K4" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -7814,7 +8812,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -7825,7 +8823,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="R4" t="n">
@@ -7833,7 +8831,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="T4" t="n">
@@ -7841,7 +8839,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -7867,27 +8865,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="J5" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -7897,7 +8895,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="O5" t="n">
@@ -7950,21 +8948,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -7973,14 +8971,14 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="O6" t="n">
@@ -8033,7 +9031,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -8043,11 +9041,11 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -8056,14 +9054,14 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M7" t="n">
         <v>1</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="O7" t="n">
@@ -8254,27 +9252,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F2" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G2" t="n">
+        <v>48</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J2" t="n">
         <v>40</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>57.1%</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>1.142857142857143</v>
-      </c>
-      <c r="J2" t="n">
-        <v>35</v>
-      </c>
       <c r="K2" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -8284,14 +9282,14 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="O2" t="n">
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -8299,7 +9297,7 @@
         </is>
       </c>
       <c r="R2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -8307,7 +9305,7 @@
         </is>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -8337,27 +9335,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="F3" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="G3" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.875</v>
+        <v>1.03448275862069</v>
       </c>
       <c r="J3" t="n">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="K3" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -8367,14 +9365,14 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="O3" t="n">
         <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -8382,7 +9380,7 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -8390,7 +9388,7 @@
         </is>
       </c>
       <c r="T3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -8420,27 +9418,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="J4" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -8450,7 +9448,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -8503,21 +9501,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F5" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="G5" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.9473684210526315</v>
+        <v>1.075471698113208</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -8526,21 +9524,21 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="M5" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="O5" t="n">
         <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -8548,7 +9546,7 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -8556,7 +9554,7 @@
         </is>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -8586,21 +9584,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -8609,14 +9607,14 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="O6" t="n">
@@ -8658,7 +9656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X10"/>
+  <dimension ref="A1:X14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -8672,7 +9670,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
@@ -8827,56 +9825,56 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PSC_G._ROSADO</t>
+          <t>PSC_M._LANDDECK</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>322806</t>
+          <t>322702</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>G. Rosado</t>
+          <t>M. Landdeck</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="I2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.833333333333333</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -8887,7 +9885,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="U2" t="n">
@@ -8895,7 +9893,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="W2" t="n">
@@ -8903,7 +9901,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
     </row>
@@ -8925,56 +9923,56 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PSC_M._LANDDECK</t>
+          <t>PSC_T._COLEMAN</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>322702</t>
+          <t>322815</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>M. Landdeck</t>
+          <t>T. Coleman</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J3" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.5</v>
+        <v>1.066666666666667</v>
       </c>
       <c r="M3" t="n">
+        <v>15</v>
+      </c>
+      <c r="N3" t="n">
+        <v>8</v>
+      </c>
+      <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>0</v>
       </c>
-      <c r="O3" t="n">
-        <v>12</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2</v>
-      </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="R3" t="n">
@@ -8985,7 +9983,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="U3" t="n">
@@ -9001,7 +9999,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
     </row>
@@ -9023,46 +10021,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PSC_T._COLEMAN</t>
+          <t>PSC_G._ROSADO</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>322815</t>
+          <t>322806</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>T. Coleman</t>
+          <t>G. Rosado</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J4" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.111111111111111</v>
+        <v>1.846153846153846</v>
       </c>
       <c r="M4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="N4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -9072,7 +10070,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="R4" t="n">
@@ -9091,7 +10089,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="W4" t="n">
@@ -9140,27 +10138,27 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J5" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.142857142857143</v>
+        <v>1.384615384615385</v>
       </c>
       <c r="M5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -9170,14 +10168,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="R5" t="n">
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -9185,7 +10183,7 @@
         </is>
       </c>
       <c r="U5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -9193,7 +10191,7 @@
         </is>
       </c>
       <c r="W5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -9219,26 +10217,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PSC_D._FRAGOSO</t>
+          <t>PSC_L._RAHAMA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>143839</t>
+          <t>296104</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>D. Fragoso</t>
+          <t>L. Rahama</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I6" t="n">
         <v>2</v>
@@ -9248,14 +10246,14 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="M6" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="N6" t="n">
         <v>2</v>
@@ -9268,7 +10266,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="R6" t="n">
@@ -9287,7 +10285,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="W6" t="n">
@@ -9317,56 +10315,56 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>PSC_L._RAHAMA</t>
+          <t>PSC_J._GREWAL</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>296104</t>
+          <t>297507</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>L. Rahama</t>
+          <t>J. Grewal</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.3333333333333333</v>
+        <v>1.125</v>
       </c>
       <c r="M7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="R7" t="n">
@@ -9385,7 +10383,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="W7" t="n">
@@ -9415,63 +10413,63 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PSC_M._LANDDECK</t>
+          <t>PSC_P._BASTOS</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>322702</t>
+          <t>155174</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>M. Landdeck</t>
+          <t>P. Bastos</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="H8" t="n">
         <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J8" t="n">
+        <v>12</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
         <v>2</v>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>0.3333333333333333</v>
-      </c>
       <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
         <v>6</v>
       </c>
-      <c r="N8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="R8" t="n">
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -9479,15 +10477,15 @@
         </is>
       </c>
       <c r="U8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -9513,63 +10511,63 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>PSC_P._BASTOS</t>
+          <t>PSC_T._COLEMAN</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>155174</t>
+          <t>322815</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>P. Bastos</t>
+          <t>T. Coleman</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I9" t="n">
         <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.4</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="M9" t="n">
+        <v>6</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4</v>
+      </c>
+      <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>0</v>
       </c>
-      <c r="O9" t="n">
-        <v>5</v>
-      </c>
-      <c r="P9" t="n">
-        <v>4</v>
-      </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="R9" t="n">
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -9577,15 +10575,15 @@
         </is>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -9611,81 +10609,473 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>PSC_J._GREWAL</t>
+          <t>PSC_M._LANDDECK</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>297507</t>
+          <t>322702</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>J. Grewal</t>
+          <t>M. Landdeck</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I10" t="n">
         <v>3</v>
       </c>
       <c r="J10" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>6</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>14.0%</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="W10" t="n">
+        <v>2</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Portimonense SC</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>PSC_D._FRAGOSO</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>143839</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>D. Fragoso</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>6</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="M11" t="n">
+        <v>6</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Portimonense SC</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>PSC_M._LANDDECK</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>322702</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>M. Landdeck</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>6</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="M12" t="n">
+        <v>6</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>14.0%</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="W12" t="n">
+        <v>2</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Portimonense SC</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>PSC_M._LANDDECK</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>322702</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>M. Landdeck</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>5</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3</v>
+      </c>
+      <c r="J13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t>60.0%</t>
         </is>
       </c>
-      <c r="L10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="M10" t="n">
+      <c r="L13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M13" t="n">
+        <v>5</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3</v>
+      </c>
+      <c r="O13" t="n">
         <v>0</v>
       </c>
-      <c r="N10" t="n">
+      <c r="P13" t="n">
         <v>0</v>
       </c>
-      <c r="O10" t="n">
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>11.6%</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="U13" t="n">
+        <v>4</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="W13" t="n">
+        <v>4</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Portimonense SC</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>PSC_P._OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>169338</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>P. Oliveira</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
         <v>5</v>
       </c>
-      <c r="P10" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>29.4%</t>
-        </is>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1</v>
-      </c>
-      <c r="T10" t="inlineStr">
+      <c r="I14" t="n">
+        <v>2</v>
+      </c>
+      <c r="J14" t="n">
+        <v>6</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>5</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="U10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="W10" t="n">
-        <v>1</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="U14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="W14" t="n">
+        <v>1</v>
+      </c>
+      <c r="X14" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -9702,7 +11092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X4"/>
+  <dimension ref="A1:X7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -9716,7 +11106,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
@@ -9890,27 +11280,27 @@
         </is>
       </c>
       <c r="H2" t="n">
+        <v>13</v>
+      </c>
+      <c r="I2" t="n">
         <v>12</v>
       </c>
-      <c r="I2" t="n">
-        <v>11</v>
-      </c>
       <c r="J2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.833333333333333</v>
+        <v>1.846153846153846</v>
       </c>
       <c r="M2" t="n">
+        <v>13</v>
+      </c>
+      <c r="N2" t="n">
         <v>12</v>
-      </c>
-      <c r="N2" t="n">
-        <v>11</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -9920,7 +11310,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -9969,17 +11359,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PSC_T._COLEMAN</t>
+          <t>PSC_G._ROSADO</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>322815</t>
+          <t>322806</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>T. Coleman</t>
+          <t>G. Rosado</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -9988,27 +11378,27 @@
         </is>
       </c>
       <c r="H3" t="n">
+        <v>13</v>
+      </c>
+      <c r="I3" t="n">
         <v>9</v>
       </c>
-      <c r="I3" t="n">
-        <v>5</v>
-      </c>
       <c r="J3" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.111111111111111</v>
+        <v>1.384615384615385</v>
       </c>
       <c r="M3" t="n">
+        <v>13</v>
+      </c>
+      <c r="N3" t="n">
         <v>9</v>
-      </c>
-      <c r="N3" t="n">
-        <v>5</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -10018,7 +11408,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="R3" t="n">
@@ -10029,7 +11419,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="U3" t="n">
@@ -10045,7 +11435,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
     </row>
@@ -10067,81 +11457,375 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>PSC_T._COLEMAN</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>322815</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>T. Coleman</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>15</v>
+      </c>
+      <c r="I4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J4" t="n">
+        <v>16</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>53.3%</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>1.066666666666667</v>
+      </c>
+      <c r="M4" t="n">
+        <v>15</v>
+      </c>
+      <c r="N4" t="n">
+        <v>8</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Portimonense SC</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PSC_J._GREWAL</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>297507</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>J. Grewal</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>9</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>8</v>
+      </c>
+      <c r="P5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Portimonense SC</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>PSC_M._LANDDECK</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>322702</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>M. Landdeck</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="H4" t="n">
-        <v>12</v>
-      </c>
-      <c r="I4" t="n">
+      <c r="H6" t="n">
+        <v>21</v>
+      </c>
+      <c r="I6" t="n">
+        <v>7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>21</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>21</v>
+      </c>
+      <c r="P6" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>48.8%</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Portimonense SC</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PSC_L._RAHAMA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>296104</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>L. Rahama</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>11</v>
+      </c>
+      <c r="I7" t="n">
         <v>2</v>
       </c>
-      <c r="J4" t="n">
-        <v>6</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M4" t="n">
+      <c r="J7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>18.2%</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0.3636363636363636</v>
+      </c>
+      <c r="M7" t="n">
+        <v>11</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2</v>
+      </c>
+      <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P7" t="n">
         <v>0</v>
       </c>
-      <c r="O4" t="n">
-        <v>12</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>46.2%</t>
-        </is>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T4" t="inlineStr">
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>55.0%</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="U4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>300.0%</t>
-        </is>
-      </c>
-      <c r="W4" t="n">
-        <v>1</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
